--- a/99_economic/Z.economic_pulse_monthly/pce_real_detail.xlsx
+++ b/99_economic/Z.economic_pulse_monthly/pce_real_detail.xlsx
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>114.308</v>
+        <v>112.902</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.04339412527155573</v>
+        <v>0.03056027164685915</v>
       </c>
       <c r="L20" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -2431,7 +2431,7 @@
         <v>0.07560114522921269</v>
       </c>
       <c r="L39" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>133.907</v>
+        <v>133.958</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>0.01031386751169472</v>
+        <v>0.01069865700920491</v>
       </c>
       <c r="L58" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>128.08</v>
+        <v>128.062</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>0.05278732183662416</v>
+        <v>0.05263936609183117</v>
       </c>
       <c r="L77" t="n">
         <v>74</v>
@@ -5336,7 +5336,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>98.312</v>
+        <v>98.206</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -5344,10 +5344,10 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>-0.02536903569906113</v>
+        <v>-0.02641988282063223</v>
       </c>
       <c r="L96" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97">
@@ -6308,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>109.094</v>
+        <v>109.148</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>0.06239348700419711</v>
+        <v>0.06291935688061789</v>
       </c>
       <c r="L115" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="116">
@@ -7280,7 +7280,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>130.384</v>
+        <v>130.863</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>0.0103057634788537</v>
+        <v>0.01401738807011021</v>
       </c>
       <c r="L134" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="135">
@@ -8252,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>114.035</v>
+        <v>113.431</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -8260,10 +8260,10 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>0.03847554867498393</v>
+        <v>0.03297513887624071</v>
       </c>
       <c r="L153" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="154">
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>145.455</v>
+        <v>145.473</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -9232,10 +9232,10 @@
         </is>
       </c>
       <c r="K172" t="n">
-        <v>0.03468512366711951</v>
+        <v>0.03481316555104241</v>
       </c>
       <c r="L172" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="173">
@@ -10196,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>102.077</v>
+        <v>102.232</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -10204,10 +10204,10 @@
         </is>
       </c>
       <c r="K191" t="n">
-        <v>0.04025395660725395</v>
+        <v>0.04183354224627278</v>
       </c>
       <c r="L191" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="192">
@@ -11168,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>107.161</v>
+        <v>106.461</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -11176,10 +11176,10 @@
         </is>
       </c>
       <c r="K210" t="n">
-        <v>-0.02507346452323111</v>
+        <v>-0.03144190616556131</v>
       </c>
       <c r="L210" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211">
@@ -12140,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>106.121</v>
+        <v>105.608</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         </is>
       </c>
       <c r="K229" t="n">
-        <v>-0.02761717139322861</v>
+        <v>-0.03231777156732485</v>
       </c>
       <c r="L229" t="n">
         <v>6</v>
@@ -13123,7 +13123,7 @@
         <v>0.0003739262253663611</v>
       </c>
       <c r="L248" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="249">
@@ -14084,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>136.686</v>
+        <v>136.718</v>
       </c>
       <c r="J267" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         </is>
       </c>
       <c r="K267" t="n">
-        <v>-0.06000880257475316</v>
+        <v>-0.05978873820592534</v>
       </c>
       <c r="L267" t="n">
         <v>2</v>
@@ -15056,7 +15056,7 @@
         <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>137.347</v>
+        <v>137.495</v>
       </c>
       <c r="J286" t="inlineStr">
         <is>
@@ -15064,10 +15064,10 @@
         </is>
       </c>
       <c r="K286" t="n">
-        <v>0.03922429121614979</v>
+        <v>0.04034412051784542</v>
       </c>
       <c r="L286" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="287">
@@ -16039,7 +16039,7 @@
         <v>0.01053765495912629</v>
       </c>
       <c r="L305" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="306">
@@ -17000,7 +17000,7 @@
         <v>0</v>
       </c>
       <c r="I324" t="n">
-        <v>108.099</v>
+        <v>108.236</v>
       </c>
       <c r="J324" t="inlineStr">
         <is>
@@ -17008,10 +17008,10 @@
         </is>
       </c>
       <c r="K324" t="n">
-        <v>0.02825100590702845</v>
+        <v>0.0295541667855681</v>
       </c>
       <c r="L324" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="325">
@@ -17972,7 +17972,7 @@
         <v>0</v>
       </c>
       <c r="I343" t="n">
-        <v>105.351</v>
+        <v>105.364</v>
       </c>
       <c r="J343" t="inlineStr">
         <is>
@@ -17980,10 +17980,10 @@
         </is>
       </c>
       <c r="K343" t="n">
-        <v>0.03311628454311877</v>
+        <v>0.03324376801929896</v>
       </c>
       <c r="L343" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="344">
@@ -18944,7 +18944,7 @@
         <v>0</v>
       </c>
       <c r="I362" t="n">
-        <v>117.856</v>
+        <v>117.735</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -18952,10 +18952,10 @@
         </is>
       </c>
       <c r="K362" t="n">
-        <v>0.008315937168474674</v>
+        <v>0.007280722767872394</v>
       </c>
       <c r="L362" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="363">
@@ -19916,7 +19916,7 @@
         <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>165.337</v>
+        <v>164.602</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="K381" t="n">
-        <v>0.1324296927439348</v>
+        <v>0.1273955151299297</v>
       </c>
       <c r="L381" t="n">
         <v>89</v>
@@ -20888,7 +20888,7 @@
         <v>0</v>
       </c>
       <c r="I400" t="n">
-        <v>81.15900000000001</v>
+        <v>80.72</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -20896,10 +20896,10 @@
         </is>
       </c>
       <c r="K400" t="n">
-        <v>-0.003034174385180499</v>
+        <v>-0.008426897280298884</v>
       </c>
       <c r="L400" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="401">
@@ -21860,7 +21860,7 @@
         <v>0</v>
       </c>
       <c r="I419" t="n">
-        <v>113.831</v>
+        <v>113.313</v>
       </c>
       <c r="J419" t="inlineStr">
         <is>
@@ -21868,10 +21868,10 @@
         </is>
       </c>
       <c r="K419" t="n">
-        <v>0.04452233916626147</v>
+        <v>0.03976912983235303</v>
       </c>
       <c r="L419" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="420">
@@ -22832,7 +22832,7 @@
         <v>0</v>
       </c>
       <c r="I438" t="n">
-        <v>125.637</v>
+        <v>125.704</v>
       </c>
       <c r="J438" t="inlineStr">
         <is>
@@ -22840,10 +22840,10 @@
         </is>
       </c>
       <c r="K438" t="n">
-        <v>0.01647235863787522</v>
+        <v>0.01701442544963228</v>
       </c>
       <c r="L438" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="439">
@@ -23804,7 +23804,7 @@
         <v>0</v>
       </c>
       <c r="I457" t="n">
-        <v>130.002</v>
+        <v>130.019</v>
       </c>
       <c r="J457" t="inlineStr">
         <is>
@@ -23812,10 +23812,10 @@
         </is>
       </c>
       <c r="K457" t="n">
-        <v>0.02658822600386945</v>
+        <v>0.02672247009120698</v>
       </c>
       <c r="L457" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="458">
@@ -24776,7 +24776,7 @@
         <v>0</v>
       </c>
       <c r="I476" t="n">
-        <v>102.37</v>
+        <v>102.547</v>
       </c>
       <c r="J476" t="inlineStr">
         <is>
@@ -24784,10 +24784,10 @@
         </is>
       </c>
       <c r="K476" t="n">
-        <v>-0.03631810822005488</v>
+        <v>-0.0346518808600369</v>
       </c>
       <c r="L476" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477">
@@ -25748,7 +25748,7 @@
         <v>0</v>
       </c>
       <c r="I495" t="n">
-        <v>174.299</v>
+        <v>169.896</v>
       </c>
       <c r="J495" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         </is>
       </c>
       <c r="K495" t="n">
-        <v>0.2552862040157866</v>
+        <v>0.223576181833895</v>
       </c>
       <c r="L495" t="n">
         <v>92</v>
@@ -27692,7 +27692,7 @@
         <v>0</v>
       </c>
       <c r="I533" t="n">
-        <v>100.211</v>
+        <v>100.129</v>
       </c>
       <c r="J533" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         </is>
       </c>
       <c r="K533" t="n">
-        <v>0.002500975380398396</v>
+        <v>0.001680655455627678</v>
       </c>
       <c r="L533" t="n">
         <v>18</v>
@@ -28664,7 +28664,7 @@
         <v>0</v>
       </c>
       <c r="I552" t="n">
-        <v>104.418</v>
+        <v>104.167</v>
       </c>
       <c r="J552" t="inlineStr">
         <is>
@@ -28672,10 +28672,10 @@
         </is>
       </c>
       <c r="K552" t="n">
-        <v>0.01380636141209379</v>
+        <v>0.01136937356790568</v>
       </c>
       <c r="L552" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="553">
@@ -29636,7 +29636,7 @@
         <v>0</v>
       </c>
       <c r="I571" t="n">
-        <v>108.543</v>
+        <v>108.519</v>
       </c>
       <c r="J571" t="inlineStr">
         <is>
@@ -29644,10 +29644,10 @@
         </is>
       </c>
       <c r="K571" t="n">
-        <v>0.009533287449543293</v>
+        <v>0.009310069011700506</v>
       </c>
       <c r="L571" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="572">
@@ -30608,7 +30608,7 @@
         <v>0</v>
       </c>
       <c r="I590" t="n">
-        <v>127.493</v>
+        <v>127.567</v>
       </c>
       <c r="J590" t="inlineStr">
         <is>
@@ -30616,10 +30616,10 @@
         </is>
       </c>
       <c r="K590" t="n">
-        <v>0.06276049481511126</v>
+        <v>0.06337734653729443</v>
       </c>
       <c r="L590" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="591">
@@ -31580,7 +31580,7 @@
         <v>0</v>
       </c>
       <c r="I609" t="n">
-        <v>118.188</v>
+        <v>118.569</v>
       </c>
       <c r="J609" t="inlineStr">
         <is>
@@ -31588,10 +31588,10 @@
         </is>
       </c>
       <c r="K609" t="n">
-        <v>0.04277395447326637</v>
+        <v>0.04613552143991528</v>
       </c>
       <c r="L609" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="610">
@@ -32552,7 +32552,7 @@
         <v>0</v>
       </c>
       <c r="I628" t="n">
-        <v>113.482</v>
+        <v>113.481</v>
       </c>
       <c r="J628" t="inlineStr">
         <is>
@@ -32560,10 +32560,10 @@
         </is>
       </c>
       <c r="K628" t="n">
-        <v>0.01169653204956767</v>
+        <v>0.01168761700989562</v>
       </c>
       <c r="L628" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="629">
@@ -33524,7 +33524,7 @@
         <v>0</v>
       </c>
       <c r="I647" t="n">
-        <v>120.928</v>
+        <v>120.923</v>
       </c>
       <c r="J647" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         </is>
       </c>
       <c r="K647" t="n">
-        <v>0.04074220699864006</v>
+        <v>0.04069917551680802</v>
       </c>
       <c r="L647" t="n">
         <v>66</v>
@@ -34496,7 +34496,7 @@
         <v>0</v>
       </c>
       <c r="I666" t="n">
-        <v>107.842</v>
+        <v>107.896</v>
       </c>
       <c r="J666" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         </is>
       </c>
       <c r="K666" t="n">
-        <v>0.05175793631442915</v>
+        <v>0.05228458575120687</v>
       </c>
       <c r="L666" t="n">
         <v>73</v>
@@ -35468,7 +35468,7 @@
         <v>0</v>
       </c>
       <c r="I685" t="n">
-        <v>108.723</v>
+        <v>108.71</v>
       </c>
       <c r="J685" t="inlineStr">
         <is>
@@ -35476,10 +35476,10 @@
         </is>
       </c>
       <c r="K685" t="n">
-        <v>0.009058256842417789</v>
+        <v>0.008937603831197016</v>
       </c>
       <c r="L685" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="686">
@@ -36440,7 +36440,7 @@
         <v>0</v>
       </c>
       <c r="I704" t="n">
-        <v>126.894</v>
+        <v>127.886</v>
       </c>
       <c r="J704" t="inlineStr">
         <is>
@@ -36448,10 +36448,10 @@
         </is>
       </c>
       <c r="K704" t="n">
-        <v>0.02133721819337908</v>
+        <v>0.02932157143662018</v>
       </c>
       <c r="L704" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="705">
@@ -37412,7 +37412,7 @@
         <v>0</v>
       </c>
       <c r="I723" t="n">
-        <v>141.243</v>
+        <v>141.17</v>
       </c>
       <c r="J723" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         </is>
       </c>
       <c r="K723" t="n">
-        <v>0.04928348030220842</v>
+        <v>0.04874116886686619</v>
       </c>
       <c r="L723" t="n">
         <v>72</v>
@@ -38395,7 +38395,7 @@
         <v>0.01732499132343435</v>
       </c>
       <c r="L742" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="743">
@@ -39356,7 +39356,7 @@
         <v>0</v>
       </c>
       <c r="I761" t="n">
-        <v>140.743</v>
+        <v>140.831</v>
       </c>
       <c r="J761" t="inlineStr">
         <is>
@@ -39364,10 +39364,10 @@
         </is>
       </c>
       <c r="K761" t="n">
-        <v>0.04434319974474454</v>
+        <v>0.04499617858971394</v>
       </c>
       <c r="L761" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="762">
@@ -40328,7 +40328,7 @@
         <v>0</v>
       </c>
       <c r="I780" t="n">
-        <v>117.948</v>
+        <v>118.022</v>
       </c>
       <c r="J780" t="inlineStr">
         <is>
@@ -40336,10 +40336,10 @@
         </is>
       </c>
       <c r="K780" t="n">
-        <v>0.01537507963017148</v>
+        <v>0.01601212100342631</v>
       </c>
       <c r="L780" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="781">
@@ -41300,7 +41300,7 @@
         <v>0</v>
       </c>
       <c r="I799" t="n">
-        <v>99.74299999999999</v>
+        <v>99.75700000000001</v>
       </c>
       <c r="J799" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>0.01251649578722969</v>
+        <v>0.0126586133387474</v>
       </c>
       <c r="L799" t="n">
         <v>35</v>
@@ -42272,7 +42272,7 @@
         <v>0</v>
       </c>
       <c r="I818" t="n">
-        <v>136.07</v>
+        <v>136.308</v>
       </c>
       <c r="J818" t="inlineStr">
         <is>
@@ -42280,10 +42280,10 @@
         </is>
       </c>
       <c r="K818" t="n">
-        <v>0.02447691971781141</v>
+        <v>0.02626883201951524</v>
       </c>
       <c r="L818" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="819">
@@ -43244,7 +43244,7 @@
         <v>0</v>
       </c>
       <c r="I837" t="n">
-        <v>120.476</v>
+        <v>120.575</v>
       </c>
       <c r="J837" t="inlineStr">
         <is>
@@ -43252,10 +43252,10 @@
         </is>
       </c>
       <c r="K837" t="n">
-        <v>0.01064534800808681</v>
+        <v>0.0114758361505618</v>
       </c>
       <c r="L837" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="838">
@@ -44216,7 +44216,7 @@
         <v>0</v>
       </c>
       <c r="I856" t="n">
-        <v>96.545</v>
+        <v>94.071</v>
       </c>
       <c r="J856" t="inlineStr">
         <is>
@@ -44224,10 +44224,10 @@
         </is>
       </c>
       <c r="K856" t="n">
-        <v>0.0007566962434697455</v>
+        <v>-0.02488805041877429</v>
       </c>
       <c r="L856" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="857">
@@ -45188,7 +45188,7 @@
         <v>0</v>
       </c>
       <c r="I875" t="n">
-        <v>122.537</v>
+        <v>122.553</v>
       </c>
       <c r="J875" t="inlineStr">
         <is>
@@ -45196,10 +45196,10 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>0.0223514492149044</v>
+        <v>0.02248494051294037</v>
       </c>
       <c r="L875" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="876">
@@ -46160,7 +46160,7 @@
         <v>0</v>
       </c>
       <c r="I894" t="n">
-        <v>108.426</v>
+        <v>107.368</v>
       </c>
       <c r="J894" t="inlineStr">
         <is>
@@ -46168,10 +46168,10 @@
         </is>
       </c>
       <c r="K894" t="n">
-        <v>0.005825711052153126</v>
+        <v>-0.003988942280932939</v>
       </c>
       <c r="L894" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="895">
@@ -47132,7 +47132,7 @@
         <v>0</v>
       </c>
       <c r="I913" t="n">
-        <v>149.749</v>
+        <v>149.949</v>
       </c>
       <c r="J913" t="inlineStr">
         <is>
@@ -47140,10 +47140,10 @@
         </is>
       </c>
       <c r="K913" t="n">
-        <v>0.01994959814739139</v>
+        <v>0.02131181038005736</v>
       </c>
       <c r="L913" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="914">
@@ -48104,7 +48104,7 @@
         <v>0</v>
       </c>
       <c r="I932" t="n">
-        <v>114.825</v>
+        <v>114.391</v>
       </c>
       <c r="J932" t="inlineStr">
         <is>
@@ -48112,10 +48112,10 @@
         </is>
       </c>
       <c r="K932" t="n">
-        <v>-0.01442844145365907</v>
+        <v>-0.01815357148988028</v>
       </c>
       <c r="L932" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="933">
@@ -49076,7 +49076,7 @@
         <v>0</v>
       </c>
       <c r="I951" t="n">
-        <v>100.07</v>
+        <v>100.198</v>
       </c>
       <c r="J951" t="inlineStr">
         <is>
@@ -49084,10 +49084,10 @@
         </is>
       </c>
       <c r="K951" t="n">
-        <v>0.03950471085626428</v>
+        <v>0.04083434614146064</v>
       </c>
       <c r="L951" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="952">
@@ -50048,7 +50048,7 @@
         <v>0</v>
       </c>
       <c r="I970" t="n">
-        <v>103.374</v>
+        <v>105.76</v>
       </c>
       <c r="J970" t="inlineStr">
         <is>
@@ -50056,10 +50056,10 @@
         </is>
       </c>
       <c r="K970" t="n">
-        <v>0.05539674112794546</v>
+        <v>0.07975660554579989</v>
       </c>
       <c r="L970" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="971">
@@ -51020,7 +51020,7 @@
         <v>0</v>
       </c>
       <c r="I989" t="n">
-        <v>121.805</v>
+        <v>121.91</v>
       </c>
       <c r="J989" t="inlineStr">
         <is>
@@ -51028,10 +51028,10 @@
         </is>
       </c>
       <c r="K989" t="n">
-        <v>0.001562307281174347</v>
+        <v>0.002425687620770445</v>
       </c>
       <c r="L989" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="990">
@@ -51992,7 +51992,7 @@
         <v>0</v>
       </c>
       <c r="I1008" t="n">
-        <v>107.243</v>
+        <v>107.477</v>
       </c>
       <c r="J1008" t="inlineStr">
         <is>
@@ -52000,10 +52000,10 @@
         </is>
       </c>
       <c r="K1008" t="n">
-        <v>0.001578347684778825</v>
+        <v>0.003763752171395573</v>
       </c>
       <c r="L1008" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1009">
@@ -52964,7 +52964,7 @@
         <v>0</v>
       </c>
       <c r="I1027" t="n">
-        <v>139.595</v>
+        <v>139.609</v>
       </c>
       <c r="J1027" t="inlineStr">
         <is>
@@ -52972,10 +52972,10 @@
         </is>
       </c>
       <c r="K1027" t="n">
-        <v>0.03262960113622926</v>
+        <v>0.0327331636880106</v>
       </c>
       <c r="L1027" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1028">
@@ -53936,7 +53936,7 @@
         <v>0</v>
       </c>
       <c r="I1046" t="n">
-        <v>123.463</v>
+        <v>124.331</v>
       </c>
       <c r="J1046" t="inlineStr">
         <is>
@@ -53944,10 +53944,10 @@
         </is>
       </c>
       <c r="K1046" t="n">
-        <v>0.005579175422306903</v>
+        <v>0.01264884588444182</v>
       </c>
       <c r="L1046" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1047">
@@ -54908,7 +54908,7 @@
         <v>0</v>
       </c>
       <c r="I1065" t="n">
-        <v>135.924</v>
+        <v>135.953</v>
       </c>
       <c r="J1065" t="inlineStr">
         <is>
@@ -54916,7 +54916,7 @@
         </is>
       </c>
       <c r="K1065" t="n">
-        <v>0.08204238246111228</v>
+        <v>0.08227324109602141</v>
       </c>
       <c r="L1065" t="n">
         <v>85</v>
@@ -55891,7 +55891,7 @@
         <v>-0.03889789303079405</v>
       </c>
       <c r="L1084" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1085">
@@ -56852,7 +56852,7 @@
         <v>0</v>
       </c>
       <c r="I1103" t="n">
-        <v>113.979</v>
+        <v>113.978</v>
       </c>
       <c r="J1103" t="inlineStr">
         <is>
@@ -56860,10 +56860,10 @@
         </is>
       </c>
       <c r="K1103" t="n">
-        <v>0.0125436406762196</v>
+        <v>0.012534757078007</v>
       </c>
       <c r="L1103" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1104">
@@ -57824,7 +57824,7 @@
         <v>0</v>
       </c>
       <c r="I1122" t="n">
-        <v>121.186</v>
+        <v>121.236</v>
       </c>
       <c r="J1122" t="inlineStr">
         <is>
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="K1122" t="n">
-        <v>0.02938153524679987</v>
+        <v>0.02980624665539766</v>
       </c>
       <c r="L1122" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1123">
@@ -58796,7 +58796,7 @@
         <v>0</v>
       </c>
       <c r="I1141" t="n">
-        <v>106.57</v>
+        <v>107.478</v>
       </c>
       <c r="J1141" t="inlineStr">
         <is>
@@ -58804,10 +58804,10 @@
         </is>
       </c>
       <c r="K1141" t="n">
-        <v>0.00830715664383308</v>
+        <v>0.01689815690875385</v>
       </c>
       <c r="L1141" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1142">
@@ -59768,7 +59768,7 @@
         <v>0</v>
       </c>
       <c r="I1160" t="n">
-        <v>144.194</v>
+        <v>144.21</v>
       </c>
       <c r="J1160" t="inlineStr">
         <is>
@@ -59776,10 +59776,10 @@
         </is>
       </c>
       <c r="K1160" t="n">
-        <v>0.05741209254574109</v>
+        <v>0.05752942470575295</v>
       </c>
       <c r="L1160" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="1161">
@@ -60740,7 +60740,7 @@
         <v>0</v>
       </c>
       <c r="I1179" t="n">
-        <v>132.537</v>
+        <v>133.084</v>
       </c>
       <c r="J1179" t="inlineStr">
         <is>
@@ -60748,7 +60748,7 @@
         </is>
       </c>
       <c r="K1179" t="n">
-        <v>0.07213234104513844</v>
+        <v>0.07655719139297856</v>
       </c>
       <c r="L1179" t="n">
         <v>83</v>
@@ -61712,7 +61712,7 @@
         <v>0</v>
       </c>
       <c r="I1198" t="n">
-        <v>118.268</v>
+        <v>118.143</v>
       </c>
       <c r="J1198" t="inlineStr">
         <is>
@@ -61720,7 +61720,7 @@
         </is>
       </c>
       <c r="K1198" t="n">
-        <v>0.007608093716719999</v>
+        <v>0.006543130990415369</v>
       </c>
       <c r="L1198" t="n">
         <v>21</v>
@@ -62684,7 +62684,7 @@
         <v>0</v>
       </c>
       <c r="I1217" t="n">
-        <v>149.555</v>
+        <v>149.057</v>
       </c>
       <c r="J1217" t="inlineStr">
         <is>
@@ -62692,7 +62692,7 @@
         </is>
       </c>
       <c r="K1217" t="n">
-        <v>0.1100678413966125</v>
+        <v>0.1063714502026334</v>
       </c>
       <c r="L1217" t="n">
         <v>86</v>
@@ -63656,7 +63656,7 @@
         <v>0</v>
       </c>
       <c r="I1236" t="n">
-        <v>109.556</v>
+        <v>109.742</v>
       </c>
       <c r="J1236" t="inlineStr">
         <is>
@@ -63664,10 +63664,10 @@
         </is>
       </c>
       <c r="K1236" t="n">
-        <v>0.05560533795827904</v>
+        <v>0.05739750445632796</v>
       </c>
       <c r="L1236" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="1237">
@@ -64628,7 +64628,7 @@
         <v>0</v>
       </c>
       <c r="I1255" t="n">
-        <v>87.42400000000001</v>
+        <v>86.58</v>
       </c>
       <c r="J1255" t="inlineStr">
         <is>
@@ -64636,10 +64636,10 @@
         </is>
       </c>
       <c r="K1255" t="n">
-        <v>-0.03249225320938465</v>
+        <v>-0.04183266932270913</v>
       </c>
       <c r="L1255" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1256">
@@ -65600,7 +65600,7 @@
         <v>0</v>
       </c>
       <c r="I1274" t="n">
-        <v>163.892</v>
+        <v>162.383</v>
       </c>
       <c r="J1274" t="inlineStr">
         <is>
@@ -65608,10 +65608,10 @@
         </is>
       </c>
       <c r="K1274" t="n">
-        <v>0.1342320894696045</v>
+        <v>0.1237888938102092</v>
       </c>
       <c r="L1274" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="1275">
@@ -66572,7 +66572,7 @@
         <v>0</v>
       </c>
       <c r="I1293" t="n">
-        <v>133.266</v>
+        <v>133.485</v>
       </c>
       <c r="J1293" t="inlineStr">
         <is>
@@ -66580,10 +66580,10 @@
         </is>
       </c>
       <c r="K1293" t="n">
-        <v>0.04433891292081982</v>
+        <v>0.04605510626293019</v>
       </c>
       <c r="L1293" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1294">
@@ -67544,7 +67544,7 @@
         <v>0</v>
       </c>
       <c r="I1312" t="n">
-        <v>174.211</v>
+        <v>174.403</v>
       </c>
       <c r="J1312" t="inlineStr">
         <is>
@@ -67552,10 +67552,10 @@
         </is>
       </c>
       <c r="K1312" t="n">
-        <v>0.03509720505751512</v>
+        <v>0.03623799790854632</v>
       </c>
       <c r="L1312" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1313">
@@ -68516,7 +68516,7 @@
         <v>0</v>
       </c>
       <c r="I1331" t="n">
-        <v>117.952</v>
+        <v>115.544</v>
       </c>
       <c r="J1331" t="inlineStr">
         <is>
@@ -68524,10 +68524,10 @@
         </is>
       </c>
       <c r="K1331" t="n">
-        <v>0.04065499717673626</v>
+        <v>0.01940993788819889</v>
       </c>
       <c r="L1331" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1332">
@@ -69488,7 +69488,7 @@
         <v>0</v>
       </c>
       <c r="I1350" t="n">
-        <v>117.322</v>
+        <v>117.385</v>
       </c>
       <c r="J1350" t="inlineStr">
         <is>
@@ -69496,10 +69496,10 @@
         </is>
       </c>
       <c r="K1350" t="n">
-        <v>0.03074071145550561</v>
+        <v>0.03129420240197511</v>
       </c>
       <c r="L1350" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="1351">
@@ -70460,7 +70460,7 @@
         <v>0</v>
       </c>
       <c r="I1369" t="n">
-        <v>126.035</v>
+        <v>127.33</v>
       </c>
       <c r="J1369" t="inlineStr">
         <is>
@@ -70468,10 +70468,10 @@
         </is>
       </c>
       <c r="K1369" t="n">
-        <v>0.01881866022132939</v>
+        <v>0.02928694415029054</v>
       </c>
       <c r="L1369" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1370">
@@ -71432,7 +71432,7 @@
         <v>0</v>
       </c>
       <c r="I1388" t="n">
-        <v>179.725</v>
+        <v>180.003</v>
       </c>
       <c r="J1388" t="inlineStr">
         <is>
@@ -71440,10 +71440,10 @@
         </is>
       </c>
       <c r="K1388" t="n">
-        <v>0.03707443739180594</v>
+        <v>0.03867859203693014</v>
       </c>
       <c r="L1388" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="1389">
@@ -72404,7 +72404,7 @@
         <v>0</v>
       </c>
       <c r="I1407" t="n">
-        <v>142.986</v>
+        <v>142.941</v>
       </c>
       <c r="J1407" t="inlineStr">
         <is>
@@ -72412,10 +72412,10 @@
         </is>
       </c>
       <c r="K1407" t="n">
-        <v>0.03742345532112479</v>
+        <v>0.03709696143018837</v>
       </c>
       <c r="L1407" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1408">
@@ -73376,7 +73376,7 @@
         <v>0</v>
       </c>
       <c r="I1426" t="n">
-        <v>323.388</v>
+        <v>323.627</v>
       </c>
       <c r="J1426" t="inlineStr">
         <is>
@@ -73384,10 +73384,10 @@
         </is>
       </c>
       <c r="K1426" t="n">
-        <v>0.1318670549364394</v>
+        <v>0.1327035616284931</v>
       </c>
       <c r="L1426" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="1427">
@@ -74348,7 +74348,7 @@
         <v>0</v>
       </c>
       <c r="I1445" t="n">
-        <v>136.67</v>
+        <v>136.999</v>
       </c>
       <c r="J1445" t="inlineStr">
         <is>
@@ -74356,10 +74356,10 @@
         </is>
       </c>
       <c r="K1445" t="n">
-        <v>0.007697639095748388</v>
+        <v>0.01012342766136287</v>
       </c>
       <c r="L1445" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1446">
@@ -75320,7 +75320,7 @@
         <v>0</v>
       </c>
       <c r="I1464" t="n">
-        <v>109.885</v>
+        <v>109.804</v>
       </c>
       <c r="J1464" t="inlineStr">
         <is>
@@ -75328,10 +75328,10 @@
         </is>
       </c>
       <c r="K1464" t="n">
-        <v>0.01590163176628301</v>
+        <v>0.01515277585170804</v>
       </c>
       <c r="L1464" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1465">
@@ -76303,7 +76303,7 @@
         <v>0.00931529447627244</v>
       </c>
       <c r="L1483" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1484">
@@ -77264,7 +77264,7 @@
         <v>0</v>
       </c>
       <c r="I1502" t="n">
-        <v>112.909</v>
+        <v>112.878</v>
       </c>
       <c r="J1502" t="inlineStr">
         <is>
@@ -77272,10 +77272,10 @@
         </is>
       </c>
       <c r="K1502" t="n">
-        <v>0.01700579169706629</v>
+        <v>0.01672656524441329</v>
       </c>
       <c r="L1502" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1503">
@@ -78247,7 +78247,7 @@
         <v>-0.001992380987519859</v>
       </c>
       <c r="L1521" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1522">
@@ -80180,7 +80180,7 @@
         <v>0</v>
       </c>
       <c r="I1559" t="n">
-        <v>128.118</v>
+        <v>128.166</v>
       </c>
       <c r="J1559" t="inlineStr">
         <is>
@@ -80188,7 +80188,7 @@
         </is>
       </c>
       <c r="K1559" t="n">
-        <v>0.05328148507444275</v>
+        <v>0.05367610184401128</v>
       </c>
       <c r="L1559" t="n">
         <v>75</v>
@@ -81152,7 +81152,7 @@
         <v>0</v>
       </c>
       <c r="I1578" t="n">
-        <v>179.639</v>
+        <v>179.763</v>
       </c>
       <c r="J1578" t="inlineStr">
         <is>
@@ -81160,7 +81160,7 @@
         </is>
       </c>
       <c r="K1578" t="n">
-        <v>0.1200556165203512</v>
+        <v>0.1208287609736634</v>
       </c>
       <c r="L1578" t="n">
         <v>87</v>
@@ -82124,7 +82124,7 @@
         <v>0</v>
       </c>
       <c r="I1597" t="n">
-        <v>105.046</v>
+        <v>104.672</v>
       </c>
       <c r="J1597" t="inlineStr">
         <is>
@@ -82132,10 +82132,10 @@
         </is>
       </c>
       <c r="K1597" t="n">
-        <v>-0.01352290441936022</v>
+        <v>-0.01703510320605528</v>
       </c>
       <c r="L1597" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1598">
@@ -83096,7 +83096,7 @@
         <v>0</v>
       </c>
       <c r="I1616" t="n">
-        <v>263.117</v>
+        <v>263.531</v>
       </c>
       <c r="J1616" t="inlineStr">
         <is>
@@ -83104,7 +83104,7 @@
         </is>
       </c>
       <c r="K1616" t="n">
-        <v>0.06202194945731798</v>
+        <v>0.06369298206667184</v>
       </c>
       <c r="L1616" t="n">
         <v>80</v>
@@ -84068,7 +84068,7 @@
         <v>0</v>
       </c>
       <c r="I1635" t="n">
-        <v>145.899</v>
+        <v>146.822</v>
       </c>
       <c r="J1635" t="inlineStr">
         <is>
@@ -84076,10 +84076,10 @@
         </is>
       </c>
       <c r="K1635" t="n">
-        <v>0.05838955386289446</v>
+        <v>0.06508523757707652</v>
       </c>
       <c r="L1635" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="1636">
@@ -85040,7 +85040,7 @@
         <v>0</v>
       </c>
       <c r="I1654" t="n">
-        <v>106.437</v>
+        <v>102.624</v>
       </c>
       <c r="J1654" t="inlineStr">
         <is>
@@ -85048,10 +85048,10 @@
         </is>
       </c>
       <c r="K1654" t="n">
-        <v>0.01762051360498695</v>
+        <v>-0.0188347323938276</v>
       </c>
       <c r="L1654" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1655">
@@ -86012,7 +86012,7 @@
         <v>0</v>
       </c>
       <c r="I1673" t="n">
-        <v>194.554</v>
+        <v>189.809</v>
       </c>
       <c r="J1673" t="inlineStr">
         <is>
@@ -86020,7 +86020,7 @@
         </is>
       </c>
       <c r="K1673" t="n">
-        <v>0.2186664161107457</v>
+        <v>0.1889442199880984</v>
       </c>
       <c r="L1673" t="n">
         <v>91</v>
@@ -86984,7 +86984,7 @@
         <v>0</v>
       </c>
       <c r="I1692" t="n">
-        <v>132.753</v>
+        <v>132.818</v>
       </c>
       <c r="J1692" t="inlineStr">
         <is>
@@ -86992,10 +86992,10 @@
         </is>
       </c>
       <c r="K1692" t="n">
-        <v>0.01224580051392699</v>
+        <v>0.01274142755838881</v>
       </c>
       <c r="L1692" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1693">
@@ -87956,7 +87956,7 @@
         <v>0</v>
       </c>
       <c r="I1711" t="n">
-        <v>120.666</v>
+        <v>120.832</v>
       </c>
       <c r="J1711" t="inlineStr">
         <is>
@@ -87964,10 +87964,10 @@
         </is>
       </c>
       <c r="K1711" t="n">
-        <v>0.007834424695977615</v>
+        <v>0.009220900708271973</v>
       </c>
       <c r="L1711" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1712">
@@ -88928,7 +88928,7 @@
         <v>0</v>
       </c>
       <c r="I1730" t="n">
-        <v>102.968</v>
+        <v>102.905</v>
       </c>
       <c r="J1730" t="inlineStr">
         <is>
@@ -88936,10 +88936,10 @@
         </is>
       </c>
       <c r="K1730" t="n">
-        <v>0.02037418741081343</v>
+        <v>0.01974988108450915</v>
       </c>
       <c r="L1730" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1731">
@@ -89509,7 +89509,7 @@
         <v>0</v>
       </c>
       <c r="L1749" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
